--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484268_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484268_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.5015</v>
+        <v>2.5893</v>
       </c>
       <c r="E2" t="n">
-        <v>6.3349</v>
+        <v>6.3954</v>
       </c>
       <c r="F2" t="n">
-        <v>-3.8333</v>
+        <v>-3.8061</v>
       </c>
       <c r="G2" t="n">
         <v>1.841</v>
@@ -610,13 +610,13 @@
         <v>2.3441</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.3312</v>
+        <v>-0.2434</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1457</v>
+        <v>-0.0851</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1855</v>
+        <v>-0.1583</v>
       </c>
       <c r="V2" t="n">
         <v>1.7731</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.288</v>
+        <v>2.294</v>
       </c>
       <c r="E3" t="n">
-        <v>1.8415</v>
+        <v>1.9021</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4464</v>
+        <v>0.392</v>
       </c>
       <c r="G3" t="n">
         <v>1.9125</v>
@@ -688,13 +688,13 @@
         <v>0.586</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.3473</v>
+        <v>-0.3412</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3026</v>
+        <v>-0.2421</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0447</v>
+        <v>-0.09909999999999999</v>
       </c>
       <c r="V3" t="n">
         <v>0.3321</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. KOTSEV</t>
+          <t>D. CAJAL PENACHO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8277</v>
+        <v>0.8594000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>2.9483</v>
+        <v>1.0985</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.1207</v>
+        <v>-0.2391</v>
       </c>
       <c r="G4" t="n">
-        <v>3.09</v>
+        <v>2.4222</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.7923</v>
+        <v>-0.2758</v>
       </c>
       <c r="I4" t="n">
-        <v>4.8823</v>
+        <v>2.698</v>
       </c>
       <c r="J4" t="n">
-        <v>6.3054</v>
+        <v>3.5354</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4783</v>
+        <v>1.1064</v>
       </c>
       <c r="L4" t="n">
-        <v>5.8271</v>
+        <v>2.4289</v>
       </c>
       <c r="M4" t="n">
-        <v>-3.2154</v>
+        <v>-1.1131</v>
       </c>
       <c r="N4" t="n">
-        <v>-2.2707</v>
+        <v>-1.3822</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.9447</v>
+        <v>0.269</v>
       </c>
       <c r="P4" t="n">
-        <v>-2.7348</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q4" t="n">
-        <v>-4.8836</v>
+        <v>-2.1488</v>
       </c>
       <c r="R4" t="n">
-        <v>2.1488</v>
+        <v>1.1721</v>
       </c>
       <c r="S4" t="n">
-        <v>1.1952</v>
+        <v>-0.3089</v>
       </c>
       <c r="T4" t="n">
-        <v>1.2493</v>
+        <v>-0.2881</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0541</v>
+        <v>-0.0208</v>
       </c>
       <c r="V4" t="n">
-        <v>0.2772</v>
+        <v>-0.2772</v>
       </c>
       <c r="W4" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. CAJAL PENACHO</t>
+          <t>M. KOTSEV</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5228</v>
+        <v>0.8498</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7346</v>
+        <v>1.9977</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.2118</v>
+        <v>-1.1479</v>
       </c>
       <c r="G5" t="n">
-        <v>2.4222</v>
+        <v>3.09</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.2758</v>
+        <v>-1.7923</v>
       </c>
       <c r="I5" t="n">
-        <v>2.698</v>
+        <v>4.8823</v>
       </c>
       <c r="J5" t="n">
-        <v>3.5354</v>
+        <v>6.3054</v>
       </c>
       <c r="K5" t="n">
-        <v>1.1064</v>
+        <v>0.4783</v>
       </c>
       <c r="L5" t="n">
-        <v>2.4289</v>
+        <v>5.8271</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.1131</v>
+        <v>-3.2154</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.3822</v>
+        <v>-2.2707</v>
       </c>
       <c r="O5" t="n">
-        <v>0.269</v>
+        <v>-0.9447</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.9767</v>
+        <v>-2.7348</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.1488</v>
+        <v>-4.8836</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1721</v>
+        <v>2.1488</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.6455</v>
+        <v>0.2174</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.652</v>
+        <v>0.2987</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0065</v>
+        <v>-0.0813</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.2772</v>
+        <v>0.2772</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1463</v>
+        <v>0.1736</v>
       </c>
       <c r="E6" t="n">
         <v>0.8027</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.6563</v>
+        <v>-0.6291</v>
       </c>
       <c r="G6" t="n">
         <v>0.0539</v>
@@ -922,13 +922,13 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0925</v>
+        <v>0.1197</v>
       </c>
       <c r="T6" t="n">
         <v>0.0743</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0182</v>
+        <v>0.0454</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>F. GASPAR AGUILAR</t>
+          <t>P. GIMENO MARTIN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.719</v>
+        <v>0.1272</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>2.7683</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.719</v>
+        <v>-2.6411</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4045</v>
+        <v>-1.2323</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2696</v>
+        <v>-2.4052</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1348</v>
+        <v>1.1729</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>2.5324</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>0.4144</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.118</v>
       </c>
       <c r="M7" t="n">
-        <v>0.4045</v>
+        <v>-3.7648</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2696</v>
+        <v>-2.8196</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1348</v>
+        <v>-0.9451000000000001</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>0.1953</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.1488</v>
       </c>
       <c r="S7" t="n">
-        <v>0.09520000000000001</v>
+        <v>-0.6637999999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>-0.1931</v>
       </c>
       <c r="U7" t="n">
-        <v>0.09520000000000001</v>
+        <v>-0.4706</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.2186</v>
+        <v>1.8279</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>2.3824</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.2186</v>
+        <v>-0.5545</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. GIMENO MARTIN</t>
+          <t>F. GASPAR AGUILAR</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.8686</v>
+        <v>-0.8279</v>
       </c>
       <c r="E8" t="n">
-        <v>2.2627</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.1313</v>
+        <v>-0.8279</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.2323</v>
+        <v>0.4045</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.4052</v>
+        <v>0.2696</v>
       </c>
       <c r="I8" t="n">
-        <v>1.1729</v>
+        <v>0.1348</v>
       </c>
       <c r="J8" t="n">
-        <v>2.5324</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.4144</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>2.118</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-3.7648</v>
+        <v>0.4045</v>
       </c>
       <c r="N8" t="n">
-        <v>-2.8196</v>
+        <v>0.2696</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.9451000000000001</v>
+        <v>0.1348</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.1488</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.6596</v>
+        <v>-0.0138</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6987</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.9609</v>
+        <v>-0.0138</v>
       </c>
       <c r="V8" t="n">
-        <v>1.8279</v>
+        <v>-1.2186</v>
       </c>
       <c r="W8" t="n">
-        <v>2.3824</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.5545</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.5592</v>
+        <v>-2.88</v>
       </c>
       <c r="E9" t="n">
-        <v>1.3066</v>
+        <v>1.3671</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.8658</v>
+        <v>-4.2471</v>
       </c>
       <c r="G9" t="n">
         <v>-2.3161</v>
@@ -1156,13 +1156,13 @@
         <v>2.5395</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3978</v>
+        <v>0.077</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1457</v>
+        <v>-0.0851</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5434</v>
+        <v>0.1622</v>
       </c>
       <c r="V9" t="n">
         <v>-0.0549</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.3503</v>
+        <v>-3.0936</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.5444</v>
+        <v>-0.3422</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.8058</v>
+        <v>-2.7514</v>
       </c>
       <c r="G10" t="n">
         <v>-2.875</v>
@@ -1234,13 +1234,13 @@
         <v>1.7581</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8194</v>
+        <v>-0.5627</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4099</v>
+        <v>-0.2077</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4095</v>
+        <v>-0.355</v>
       </c>
       <c r="V10" t="n">
         <v>-1.2186</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.2107999999999999</v>
+        <v>0.09180000000000055</v>
       </c>
       <c r="E11" t="n">
-        <v>15.6869</v>
+        <v>15.9896</v>
       </c>
       <c r="F11" t="n">
-        <v>-15.8976</v>
+        <v>-15.8977</v>
       </c>
       <c r="G11" t="n">
         <v>3.300699999999999</v>
@@ -1312,13 +1312,13 @@
         <v>12.6974</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.0223</v>
+        <v>-1.7197</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.031</v>
+        <v>-0.7282</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.9913999999999999</v>
+        <v>-0.9913</v>
       </c>
       <c r="V11" t="n">
         <v>1.441</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>3.5895</v>
+        <v>3.1837</v>
       </c>
       <c r="E12" t="n">
-        <v>5.4103</v>
+        <v>5.0058</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.8208</v>
+        <v>-1.8222</v>
       </c>
       <c r="G12" t="n">
         <v>2.2932</v>
@@ -1390,13 +1390,13 @@
         <v>1.3674</v>
       </c>
       <c r="S12" t="n">
-        <v>1.2023</v>
+        <v>0.7965</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9245</v>
+        <v>0.5201</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2778</v>
+        <v>0.2764</v>
       </c>
       <c r="V12" t="n">
         <v>-1.2735</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.6904</v>
+        <v>1.9379</v>
       </c>
       <c r="E13" t="n">
-        <v>1.5289</v>
+        <v>1.8322</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1615</v>
+        <v>0.1057</v>
       </c>
       <c r="G13" t="n">
         <v>0.8355</v>
@@ -1468,13 +1468,13 @@
         <v>1.5627</v>
       </c>
       <c r="S13" t="n">
-        <v>0.0269</v>
+        <v>0.2744</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4099</v>
+        <v>-0.1065</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4368</v>
+        <v>0.381</v>
       </c>
       <c r="V13" t="n">
         <v>1.2186</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>I. BELVER EDO</t>
+          <t>A. REAL LOPEZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.4976</v>
+        <v>1.0613</v>
       </c>
       <c r="E14" t="n">
-        <v>2.2657</v>
+        <v>3.9456</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.7681</v>
+        <v>-2.8843</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.8688</v>
+        <v>1.1196</v>
       </c>
       <c r="H14" t="n">
-        <v>0.6152</v>
+        <v>1.4157</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.484</v>
+        <v>-0.2961</v>
       </c>
       <c r="J14" t="n">
-        <v>0.9644</v>
+        <v>4.9208</v>
       </c>
       <c r="K14" t="n">
-        <v>0.9644</v>
+        <v>1.8445</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>3.0764</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.8332</v>
+        <v>-3.8012</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.3492</v>
+        <v>-0.4287</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.484</v>
+        <v>-3.3725</v>
       </c>
       <c r="P14" t="n">
-        <v>0.586</v>
+        <v>1.1721</v>
       </c>
       <c r="Q14" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R14" t="n">
-        <v>1.5627</v>
+        <v>2.1488</v>
       </c>
       <c r="S14" t="n">
-        <v>1.171</v>
+        <v>0.2655</v>
       </c>
       <c r="T14" t="n">
-        <v>1.0594</v>
+        <v>0.0015</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1117</v>
+        <v>0.264</v>
       </c>
       <c r="V14" t="n">
-        <v>0.6093</v>
+        <v>-1.4959</v>
       </c>
       <c r="W14" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.6093</v>
+        <v>-1.4959</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. REAL LOPEZ</t>
+          <t>I. BELVER EDO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4832</v>
+        <v>0.8507</v>
       </c>
       <c r="E15" t="n">
-        <v>3.3389</v>
+        <v>1.4568</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.8557</v>
+        <v>-0.6061</v>
       </c>
       <c r="G15" t="n">
-        <v>1.1196</v>
+        <v>-0.8688</v>
       </c>
       <c r="H15" t="n">
-        <v>1.4157</v>
+        <v>0.6152</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2961</v>
+        <v>-1.484</v>
       </c>
       <c r="J15" t="n">
-        <v>4.9208</v>
+        <v>0.9644</v>
       </c>
       <c r="K15" t="n">
-        <v>1.8445</v>
+        <v>0.9644</v>
       </c>
       <c r="L15" t="n">
-        <v>3.0764</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>-3.8012</v>
+        <v>-1.8332</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.4287</v>
+        <v>-0.3492</v>
       </c>
       <c r="O15" t="n">
-        <v>-3.3725</v>
+        <v>-1.484</v>
       </c>
       <c r="P15" t="n">
-        <v>1.1721</v>
+        <v>0.586</v>
       </c>
       <c r="Q15" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R15" t="n">
-        <v>2.1488</v>
+        <v>1.5627</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.3126</v>
+        <v>0.5241</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6052</v>
+        <v>0.2504</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2926</v>
+        <v>0.2737</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.4959</v>
+        <v>0.6093</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.4959</v>
+        <v>-0.6093</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>C. MARZO CHECA</t>
+          <t>A. SOTO CAPARROS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1834</v>
+        <v>0.5397999999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>2.0124</v>
+        <v>4.8776</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.1958</v>
+        <v>-4.3379</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.5221</v>
+        <v>2.5111</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.2929</v>
+        <v>5.0742</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.2292</v>
+        <v>-2.5632</v>
       </c>
       <c r="J16" t="n">
-        <v>1.2694</v>
+        <v>6.9912</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.1203</v>
+        <v>6.1819</v>
       </c>
       <c r="L16" t="n">
-        <v>1.3897</v>
+        <v>0.8093</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.7915</v>
+        <v>-4.4802</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.1727</v>
+        <v>-1.1077</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.6188</v>
+        <v>-3.3725</v>
       </c>
       <c r="P16" t="n">
-        <v>1.5627</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5627</v>
+        <v>1.7581</v>
       </c>
       <c r="S16" t="n">
-        <v>0.3853</v>
+        <v>-0.335</v>
       </c>
       <c r="T16" t="n">
-        <v>0.743</v>
+        <v>-0.1602</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3577</v>
+        <v>-0.1748</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.6093</v>
+        <v>-1.441</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.6093</v>
+        <v>-1.441</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. SOTO CAPARROS</t>
+          <t>C. MARZO CHECA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.4002</v>
+        <v>-0.1807</v>
       </c>
       <c r="E17" t="n">
-        <v>4.3721</v>
+        <v>1.6079</v>
       </c>
       <c r="F17" t="n">
-        <v>-4.7723</v>
+        <v>-1.7886</v>
       </c>
       <c r="G17" t="n">
-        <v>2.5111</v>
+        <v>-1.5221</v>
       </c>
       <c r="H17" t="n">
-        <v>5.0742</v>
+        <v>-1.2929</v>
       </c>
       <c r="I17" t="n">
-        <v>-2.5632</v>
+        <v>-0.2292</v>
       </c>
       <c r="J17" t="n">
-        <v>6.9912</v>
+        <v>1.2694</v>
       </c>
       <c r="K17" t="n">
-        <v>6.1819</v>
+        <v>-0.1203</v>
       </c>
       <c r="L17" t="n">
-        <v>0.8093</v>
+        <v>1.3897</v>
       </c>
       <c r="M17" t="n">
-        <v>-4.4802</v>
+        <v>-2.7915</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.1077</v>
+        <v>-1.1727</v>
       </c>
       <c r="O17" t="n">
-        <v>-3.3725</v>
+        <v>-1.6188</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.1953</v>
+        <v>1.5627</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.7581</v>
+        <v>1.5627</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.2749</v>
+        <v>0.388</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6657</v>
+        <v>0.3385</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.6092</v>
+        <v>0.0495</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.441</v>
+        <v>-0.6093</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.441</v>
+        <v>-0.6093</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ MARIN</t>
+          <t>J. AURO GARRIGA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.4273</v>
+        <v>-0.7858000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.1152</v>
+        <v>1.564</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6879</v>
+        <v>-2.3499</v>
       </c>
       <c r="G18" t="n">
-        <v>-4.2123</v>
+        <v>-0.285</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.0417</v>
+        <v>1.2387</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.1705</v>
+        <v>-1.5237</v>
       </c>
       <c r="J18" t="n">
-        <v>-3.5139</v>
+        <v>2.7017</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.9389</v>
+        <v>2.067</v>
       </c>
       <c r="L18" t="n">
-        <v>-2.575</v>
+        <v>0.6346000000000001</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.6984</v>
+        <v>-2.9866</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.1028</v>
+        <v>-0.8283</v>
       </c>
       <c r="O18" t="n">
-        <v>0.4045</v>
+        <v>-2.1583</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.3907</v>
+        <v>0.1953</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5627</v>
+        <v>1.1721</v>
       </c>
       <c r="S18" t="n">
-        <v>1.0742</v>
+        <v>-0.1417</v>
       </c>
       <c r="T18" t="n">
-        <v>0.6962</v>
+        <v>-0.1609</v>
       </c>
       <c r="U18" t="n">
-        <v>0.378</v>
+        <v>0.0192</v>
       </c>
       <c r="V18" t="n">
-        <v>3.1014</v>
+        <v>-0.5545</v>
       </c>
       <c r="W18" t="n">
-        <v>3.6559</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
         <v>-0.5545</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. AURO GARRIGA</t>
+          <t>A. REYES QUEZADA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.0139</v>
+        <v>-0.7875</v>
       </c>
       <c r="E19" t="n">
-        <v>1.3618</v>
+        <v>-0.4419</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.3757</v>
+        <v>-0.3456</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.285</v>
+        <v>-1.0973</v>
       </c>
       <c r="H19" t="n">
-        <v>1.2387</v>
+        <v>-1.9609</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.5237</v>
+        <v>0.8636</v>
       </c>
       <c r="J19" t="n">
-        <v>2.7017</v>
+        <v>0.5456</v>
       </c>
       <c r="K19" t="n">
-        <v>2.067</v>
+        <v>-1.2625</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6346000000000001</v>
+        <v>1.8081</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.9866</v>
+        <v>-1.6429</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.8283</v>
+        <v>-0.6984</v>
       </c>
       <c r="O19" t="n">
-        <v>-2.1583</v>
+        <v>-0.9445</v>
       </c>
       <c r="P19" t="n">
-        <v>0.1953</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9767</v>
+        <v>-2.9301</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1721</v>
+        <v>1.9534</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3698</v>
+        <v>0.7869</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3631</v>
+        <v>0.2244</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0067</v>
+        <v>0.5625</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.5545</v>
+        <v>0.4996</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.7182</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.5545</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. REYES QUEZADA</t>
+          <t>J. RODRIGUEZ MARIN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.0428</v>
+        <v>-0.8253</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.6442</v>
+        <v>-1.6208</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3987</v>
+        <v>0.7954</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.0973</v>
+        <v>-4.2123</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.9609</v>
+        <v>-2.0417</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8636</v>
+        <v>-2.1705</v>
       </c>
       <c r="J20" t="n">
-        <v>0.5456</v>
+        <v>-3.5139</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.2625</v>
+        <v>-0.9389</v>
       </c>
       <c r="L20" t="n">
-        <v>1.8081</v>
+        <v>-2.575</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.6429</v>
+        <v>-0.6984</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.6984</v>
+        <v>-1.1028</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.9445</v>
+        <v>0.4045</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.9767</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.9301</v>
+        <v>-1.9534</v>
       </c>
       <c r="R20" t="n">
-        <v>1.9534</v>
+        <v>1.5627</v>
       </c>
       <c r="S20" t="n">
-        <v>0.5316</v>
+        <v>0.6762</v>
       </c>
       <c r="T20" t="n">
-        <v>0.0221</v>
+        <v>0.1906</v>
       </c>
       <c r="U20" t="n">
-        <v>0.5094</v>
+        <v>0.4855</v>
       </c>
       <c r="V20" t="n">
-        <v>0.4996</v>
+        <v>3.1014</v>
       </c>
       <c r="W20" t="n">
-        <v>1.7182</v>
+        <v>3.6559</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.2186</v>
+        <v>-0.5545</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.9821</v>
+        <v>-3.435</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.6329</v>
+        <v>-2.3296</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.3492</v>
+        <v>-1.1054</v>
       </c>
       <c r="G21" t="n">
         <v>-2.0747</v>
@@ -2092,13 +2092,13 @@
         <v>0.9767</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4116</v>
+        <v>0.1356</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4099</v>
+        <v>-0.1065</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0017</v>
+        <v>0.2421</v>
       </c>
       <c r="V21" t="n">
         <v>-1.4959</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.2110000000000003</v>
+        <v>1.559099999999999</v>
       </c>
       <c r="E22" t="n">
-        <v>15.8978</v>
+        <v>15.8976</v>
       </c>
       <c r="F22" t="n">
-        <v>-15.6869</v>
+        <v>-14.3389</v>
       </c>
       <c r="G22" t="n">
         <v>-3.3008</v>
@@ -2155,13 +2155,13 @@
         <v>-23.1477</v>
       </c>
       <c r="N22" t="n">
-        <v>-7.6335</v>
+        <v>-7.633500000000001</v>
       </c>
       <c r="O22" t="n">
         <v>-15.5141</v>
       </c>
       <c r="P22" t="n">
-        <v>2.930099999999999</v>
+        <v>2.9301</v>
       </c>
       <c r="Q22" t="n">
         <v>-12.6971</v>
@@ -2170,22 +2170,22 @@
         <v>15.6273</v>
       </c>
       <c r="S22" t="n">
-        <v>2.0224</v>
+        <v>3.3705</v>
       </c>
       <c r="T22" t="n">
         <v>0.9914000000000001</v>
       </c>
       <c r="U22" t="n">
-        <v>1.031</v>
+        <v>2.3791</v>
       </c>
       <c r="V22" t="n">
         <v>-1.4412</v>
       </c>
       <c r="W22" t="n">
-        <v>7.756399999999999</v>
+        <v>7.7564</v>
       </c>
       <c r="X22" t="n">
-        <v>-9.197600000000001</v>
+        <v>-9.1976</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484268_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484268_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X22"/>
+  <dimension ref="A1:Y23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-1.2186</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484268_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-0.5545</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484268_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-0.2772</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484268_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484268_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484268_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-0.5545</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484268_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-1.2186</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484268_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-2.7145</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484268_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-1.2186</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484268_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,11 +1379,12 @@
       <c r="X11" t="n">
         <v>-7.756500000000001</v>
       </c>
+      <c r="Y11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>G. VIÑALLONGA BLANCO</t>
+          <t>G. VINALLONGA BLANCO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,28 +1396,28 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>3.1837</v>
+        <v>2.8767</v>
       </c>
       <c r="E12" t="n">
-        <v>5.0058</v>
+        <v>4.6988</v>
       </c>
       <c r="F12" t="n">
         <v>-1.8222</v>
       </c>
       <c r="G12" t="n">
-        <v>2.2932</v>
+        <v>1.9862</v>
       </c>
       <c r="H12" t="n">
-        <v>3.8041</v>
+        <v>3.4971</v>
       </c>
       <c r="I12" t="n">
         <v>-1.5109</v>
       </c>
       <c r="J12" t="n">
-        <v>4.5406</v>
+        <v>4.2336</v>
       </c>
       <c r="K12" t="n">
-        <v>4.2978</v>
+        <v>3.9908</v>
       </c>
       <c r="L12" t="n">
         <v>0.2428</v>
@@ -1406,6 +1457,11 @@
       </c>
       <c r="X12" t="n">
         <v>-1.2186</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484268_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -1485,6 +1541,11 @@
       <c r="X13" t="n">
         <v>0</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484268_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>-1.4959</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484268_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-0.6093</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484268_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,11 +1790,16 @@
       <c r="X16" t="n">
         <v>-1.441</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484268_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>C. MARZO CHECA</t>
+          <t>G. VIÑALLONGA BLANCO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1811,78 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1807</v>
+        <v>0.307</v>
       </c>
       <c r="E17" t="n">
-        <v>1.6079</v>
+        <v>0.307</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.7886</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.5221</v>
+        <v>0.307</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.2929</v>
+        <v>0.307</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.2292</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>1.2694</v>
+        <v>0.307</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.1203</v>
+        <v>0.307</v>
       </c>
       <c r="L17" t="n">
-        <v>1.3897</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.7915</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.1727</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.6188</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1.5627</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5627</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0.388</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>0.3385</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0495</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.6093</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.6093</v>
+        <v>0</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484268_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. AURO GARRIGA</t>
+          <t>C. MARZO CHECA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1894,78 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.7858000000000001</v>
+        <v>-0.1807</v>
       </c>
       <c r="E18" t="n">
-        <v>1.564</v>
+        <v>1.6079</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.3499</v>
+        <v>-1.7886</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.285</v>
+        <v>-1.5221</v>
       </c>
       <c r="H18" t="n">
-        <v>1.2387</v>
+        <v>-1.2929</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.5237</v>
+        <v>-0.2292</v>
       </c>
       <c r="J18" t="n">
-        <v>2.7017</v>
+        <v>1.2694</v>
       </c>
       <c r="K18" t="n">
-        <v>2.067</v>
+        <v>-0.1203</v>
       </c>
       <c r="L18" t="n">
-        <v>0.6346000000000001</v>
+        <v>1.3897</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.9866</v>
+        <v>-2.7915</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.8283</v>
+        <v>-1.1727</v>
       </c>
       <c r="O18" t="n">
-        <v>-2.1583</v>
+        <v>-1.6188</v>
       </c>
       <c r="P18" t="n">
-        <v>0.1953</v>
+        <v>1.5627</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1721</v>
+        <v>1.5627</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1417</v>
+        <v>0.388</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1609</v>
+        <v>0.3385</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0192</v>
+        <v>0.0495</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.5545</v>
+        <v>-0.6093</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.5545</v>
+        <v>-0.6093</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484268_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. REYES QUEZADA</t>
+          <t>J. AURO GARRIGA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1977,78 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.7875</v>
+        <v>-0.7858000000000001</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.4419</v>
+        <v>1.564</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.3456</v>
+        <v>-2.3499</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.0973</v>
+        <v>-0.285</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.9609</v>
+        <v>1.2387</v>
       </c>
       <c r="I19" t="n">
-        <v>0.8636</v>
+        <v>-1.5237</v>
       </c>
       <c r="J19" t="n">
-        <v>0.5456</v>
+        <v>2.7017</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.2625</v>
+        <v>2.067</v>
       </c>
       <c r="L19" t="n">
-        <v>1.8081</v>
+        <v>0.6346000000000001</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.6429</v>
+        <v>-2.9866</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.6984</v>
+        <v>-0.8283</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.9445</v>
+        <v>-2.1583</v>
       </c>
       <c r="P19" t="n">
+        <v>0.1953</v>
+      </c>
+      <c r="Q19" t="n">
         <v>-0.9767</v>
       </c>
-      <c r="Q19" t="n">
-        <v>-2.9301</v>
-      </c>
       <c r="R19" t="n">
-        <v>1.9534</v>
+        <v>1.1721</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7869</v>
+        <v>-0.1417</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2244</v>
+        <v>-0.1609</v>
       </c>
       <c r="U19" t="n">
-        <v>0.5625</v>
+        <v>0.0192</v>
       </c>
       <c r="V19" t="n">
-        <v>0.4996</v>
+        <v>-0.5545</v>
       </c>
       <c r="W19" t="n">
-        <v>1.7182</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.2186</v>
+        <v>-0.5545</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484268_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ MARIN</t>
+          <t>A. REYES QUEZADA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.8253</v>
+        <v>-0.7875</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.6208</v>
+        <v>-0.4419</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7954</v>
+        <v>-0.3456</v>
       </c>
       <c r="G20" t="n">
-        <v>-4.2123</v>
+        <v>-1.0973</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.0417</v>
+        <v>-1.9609</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.1705</v>
+        <v>0.8636</v>
       </c>
       <c r="J20" t="n">
-        <v>-3.5139</v>
+        <v>0.5456</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.9389</v>
+        <v>-1.2625</v>
       </c>
       <c r="L20" t="n">
-        <v>-2.575</v>
+        <v>1.8081</v>
       </c>
       <c r="M20" t="n">
+        <v>-1.6429</v>
+      </c>
+      <c r="N20" t="n">
         <v>-0.6984</v>
       </c>
-      <c r="N20" t="n">
-        <v>-1.1028</v>
-      </c>
       <c r="O20" t="n">
-        <v>0.4045</v>
+        <v>-0.9445</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.3907</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.9534</v>
+        <v>-2.9301</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5627</v>
+        <v>1.9534</v>
       </c>
       <c r="S20" t="n">
-        <v>0.6762</v>
+        <v>0.7869</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1906</v>
+        <v>0.2244</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4855</v>
+        <v>0.5625</v>
       </c>
       <c r="V20" t="n">
-        <v>3.1014</v>
+        <v>0.4996</v>
       </c>
       <c r="W20" t="n">
-        <v>3.6559</v>
+        <v>1.7182</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.5545</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484268_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. PAGES SAUQUE</t>
+          <t>J. RODRIGUEZ MARIN</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.435</v>
+        <v>-0.8253</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.3296</v>
+        <v>-1.6208</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.1054</v>
+        <v>0.7954</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.0747</v>
+        <v>-4.2123</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.0366</v>
+        <v>-2.0417</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.0381</v>
+        <v>-2.1705</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.2463</v>
+        <v>-3.5139</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0614</v>
+        <v>-0.9389</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.3077</v>
+        <v>-2.575</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.8283</v>
+        <v>-0.6984</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.098</v>
+        <v>-1.1028</v>
       </c>
       <c r="O21" t="n">
-        <v>0.2696</v>
+        <v>0.4045</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R21" t="n">
-        <v>0.9767</v>
+        <v>1.5627</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1356</v>
+        <v>0.6762</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1065</v>
+        <v>0.1906</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2421</v>
+        <v>0.4855</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.4959</v>
+        <v>3.1014</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>3.6559</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.4959</v>
+        <v>-0.5545</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484268_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>M. PAGES SAUQUE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,68 +2226,152 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>1.559099999999999</v>
+        <v>-3.435</v>
       </c>
       <c r="E22" t="n">
+        <v>-2.3296</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-1.1054</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-2.0747</v>
+      </c>
+      <c r="H22" t="n">
+        <v>-1.0366</v>
+      </c>
+      <c r="I22" t="n">
+        <v>-1.0381</v>
+      </c>
+      <c r="J22" t="n">
+        <v>-1.2463</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.0614</v>
+      </c>
+      <c r="L22" t="n">
+        <v>-1.3077</v>
+      </c>
+      <c r="M22" t="n">
+        <v>-0.8283</v>
+      </c>
+      <c r="N22" t="n">
+        <v>-1.098</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0.2696</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0.9767</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0.1356</v>
+      </c>
+      <c r="T22" t="n">
+        <v>-0.1065</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0.2421</v>
+      </c>
+      <c r="V22" t="n">
+        <v>-1.4959</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>-1.4959</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484268_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>DM GROUP MOLLET</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1.5591</v>
+      </c>
+      <c r="E23" t="n">
         <v>15.8976</v>
       </c>
-      <c r="F22" t="n">
+      <c r="F23" t="n">
         <v>-14.3389</v>
       </c>
-      <c r="G22" t="n">
+      <c r="G23" t="n">
         <v>-3.3008</v>
       </c>
-      <c r="H22" t="n">
+      <c r="H23" t="n">
         <v>7.4879</v>
       </c>
-      <c r="I22" t="n">
+      <c r="I23" t="n">
         <v>-10.7887</v>
       </c>
-      <c r="J22" t="n">
+      <c r="J23" t="n">
         <v>19.8471</v>
       </c>
-      <c r="K22" t="n">
+      <c r="K23" t="n">
         <v>15.1214</v>
       </c>
-      <c r="L22" t="n">
+      <c r="L23" t="n">
         <v>4.7257</v>
       </c>
-      <c r="M22" t="n">
+      <c r="M23" t="n">
         <v>-23.1477</v>
       </c>
-      <c r="N22" t="n">
+      <c r="N23" t="n">
         <v>-7.633500000000001</v>
       </c>
-      <c r="O22" t="n">
+      <c r="O23" t="n">
         <v>-15.5141</v>
       </c>
-      <c r="P22" t="n">
-        <v>2.9301</v>
-      </c>
-      <c r="Q22" t="n">
+      <c r="P23" t="n">
+        <v>2.930099999999999</v>
+      </c>
+      <c r="Q23" t="n">
         <v>-12.6971</v>
       </c>
-      <c r="R22" t="n">
+      <c r="R23" t="n">
         <v>15.6273</v>
       </c>
-      <c r="S22" t="n">
+      <c r="S23" t="n">
         <v>3.3705</v>
       </c>
-      <c r="T22" t="n">
+      <c r="T23" t="n">
         <v>0.9914000000000001</v>
       </c>
-      <c r="U22" t="n">
+      <c r="U23" t="n">
         <v>2.3791</v>
       </c>
-      <c r="V22" t="n">
+      <c r="V23" t="n">
         <v>-1.4412</v>
       </c>
-      <c r="W22" t="n">
+      <c r="W23" t="n">
         <v>7.7564</v>
       </c>
-      <c r="X22" t="n">
+      <c r="X23" t="n">
         <v>-9.1976</v>
       </c>
+      <c r="Y23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
